--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_advertising.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_advertising.xlsx
@@ -587,32 +587,35 @@
           <t>Advertising</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.207</v>
+      </c>
       <c r="G2">
-        <v>-5.823754789272031</v>
+        <v>-1.591078066914498</v>
       </c>
       <c r="H2">
-        <v>-5.823754789272031</v>
+        <v>-1.591078066914498</v>
       </c>
       <c r="I2">
-        <v>-5.555555555555555</v>
+        <v>-1.817843866171003</v>
       </c>
       <c r="J2">
-        <v>-5.555555555555555</v>
+        <v>-1.817843866171003</v>
       </c>
       <c r="K2">
-        <v>-1.33</v>
+        <v>-0.196</v>
       </c>
       <c r="L2">
-        <v>-5.095785440613027</v>
+        <v>-0.7286245353159851</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.034</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.02982456140350878</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.173469387755102</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,67 +627,64 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.034</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="V2">
-        <v>0.008648648648648649</v>
+        <v>0.008771929824561405</v>
       </c>
       <c r="W2">
-        <v>1.4</v>
+        <v>0.1798165137614679</v>
       </c>
       <c r="X2">
-        <v>0.1207715999855164</v>
+        <v>0.1077452304313038</v>
       </c>
       <c r="Y2">
-        <v>1.279228400014484</v>
+        <v>0.07207128333016406</v>
       </c>
       <c r="AB2">
-        <v>0.1207420821974702</v>
+        <v>0.1061676671302028</v>
       </c>
       <c r="AD2">
-        <v>0.001</v>
+        <v>0.039</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.001</v>
+        <v>0.039</v>
       </c>
       <c r="AG2">
-        <v>-0.015</v>
+        <v>0.029</v>
       </c>
       <c r="AH2">
-        <v>0.0005402485143165856</v>
+        <v>0.03307888040712469</v>
       </c>
       <c r="AI2">
-        <v>-0.0006540222367560496</v>
+        <v>-0.02997694081475788</v>
       </c>
       <c r="AJ2">
-        <v>-0.008174386920980926</v>
+        <v>0.02480752780153978</v>
       </c>
       <c r="AK2">
-        <v>0.009708737864077671</v>
+        <v>-0.0221205186880244</v>
       </c>
       <c r="AL2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>-0.0006802721088435375</v>
-      </c>
-      <c r="AO2">
-        <v>-1450</v>
+        <v>-0.07692307692307693</v>
       </c>
       <c r="AP2">
-        <v>0.01020408163265306</v>
-      </c>
-      <c r="AQ2">
-        <v>-1450</v>
+        <v>-0.05719921104536489</v>
       </c>
     </row>
     <row r="3">
@@ -703,32 +703,35 @@
           <t>Advertising</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.207</v>
+      </c>
       <c r="G3">
-        <v>-5.823754789272031</v>
+        <v>-1.591078066914498</v>
       </c>
       <c r="H3">
-        <v>-5.823754789272031</v>
+        <v>-1.591078066914498</v>
       </c>
       <c r="I3">
-        <v>-5.555555555555555</v>
+        <v>-1.817843866171003</v>
       </c>
       <c r="J3">
-        <v>-5.555555555555555</v>
+        <v>-1.817843866171003</v>
       </c>
       <c r="K3">
-        <v>-1.33</v>
+        <v>-0.196</v>
       </c>
       <c r="L3">
-        <v>-5.095785440613027</v>
+        <v>-0.7286245353159851</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.034</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.02982456140350878</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.173469387755102</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -740,67 +743,64 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.034</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="V3">
-        <v>0.008648648648648649</v>
+        <v>0.008771929824561405</v>
       </c>
       <c r="W3">
-        <v>1.4</v>
+        <v>0.1798165137614679</v>
       </c>
       <c r="X3">
-        <v>0.1207715999855164</v>
+        <v>0.1077452304313038</v>
       </c>
       <c r="Y3">
-        <v>1.279228400014484</v>
+        <v>0.07207128333016406</v>
       </c>
       <c r="AB3">
-        <v>0.1207420821974702</v>
+        <v>0.1061676671302028</v>
       </c>
       <c r="AD3">
-        <v>0.001</v>
+        <v>0.039</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.001</v>
+        <v>0.039</v>
       </c>
       <c r="AG3">
-        <v>-0.015</v>
+        <v>0.029</v>
       </c>
       <c r="AH3">
-        <v>0.0005402485143165856</v>
+        <v>0.03307888040712469</v>
       </c>
       <c r="AI3">
-        <v>-0.0006540222367560496</v>
+        <v>-0.02997694081475788</v>
       </c>
       <c r="AJ3">
-        <v>-0.008174386920980926</v>
+        <v>0.02480752780153978</v>
       </c>
       <c r="AK3">
-        <v>0.009708737864077671</v>
+        <v>-0.0221205186880244</v>
       </c>
       <c r="AL3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>-0.0006802721088435375</v>
-      </c>
-      <c r="AO3">
-        <v>-1450</v>
+        <v>-0.07692307692307693</v>
       </c>
       <c r="AP3">
-        <v>0.01020408163265306</v>
-      </c>
-      <c r="AQ3">
-        <v>-1450</v>
+        <v>-0.05719921104536489</v>
       </c>
     </row>
   </sheetData>
